--- a/processed_ruby_restored_xlsx/sc021_２日目.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc021_２日目.ss.xlsx
@@ -544,8 +544,8 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>When I woke up I rolled over onto all fours and sprang
-up as if bouncing.</t>
+          <t>When I woke up I rolled over onto all fours and
+sprang up as if bouncing.</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -749,8 +749,8 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>The warmth is gone, but the scent that proves she wore
-these clothes still rises—</t>
+          <t>The warmth is gone, but the scent that proves she
+wore these clothes still rises—</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -841,8 +841,8 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>However, at some point a rule developed that underwear
-should be washed by the girls themselves.</t>
+          <t>However, at some point a rule developed that
+underwear should be washed by the girls themselves.</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -858,8 +858,8 @@
       <c r="B26" s="1" t="inlineStr">
         <is>
           <t>Well, they're girls, so I get that they'd be
-embarrassed to have their underwear washed, but it's a
-little disappointing.</t>
+embarrassed to have their underwear washed, but it's
+a little disappointing.</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -967,9 +967,9 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>I'd like to spend more time on it, but with the little
-time available in the morning, this is about as much
-as I can manage.</t>
+          <t>I'd like to spend more time on it, but with the
+little time available in the morning, this is about
+as much as I can manage.</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1016,9 +1016,9 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>I can't make something elaborate like an Okosama lunch
-first thing in the morning, but it still needs some
-color.</t>
+          <t>I can't make something elaborate like an Okosama
+lunch first thing in the morning, but it still needs
+some color.</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1144,8 +1144,8 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>Once the cleaning is done, I start preparing breakfast
-while keeping an eye on the laundry.</t>
+          <t>Once the cleaning is done, I start preparing
+breakfast while keeping an eye on the laundry.</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1256,7 +1256,8 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>This morning, fluffy scrambled eggs are the main dish.</t>
+          <t>This morning, fluffy scrambled eggs are the main
+dish.</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1272,8 +1273,8 @@
       <c r="B52" s="1" t="inlineStr">
         <is>
           <t>The other ingredients were already prepared and just
-needed reheating or plating, but egg dishes, once they
-cool, never get fluffy again.</t>
+needed reheating or plating, but egg dishes, once
+they cool, never get fluffy again.</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1321,8 +1322,9 @@
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>Take out the ingredients you prepared here beforehand,
-and get ready to cook them at the same time.</t>
+          <t>Take out the ingredients you prepared here
+beforehand, and get ready to cook them at the same
+time.</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1569,8 +1571,8 @@
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan is full of energy this morning, but Rin-chan
-is kind of out of it.</t>
+          <t>Miru-chan is full of energy this morning, but
+Rin-chan is kind of out of it.</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1859,8 +1861,8 @@
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan said 'food' to match Miru-chan, then promptly
-sat down at the table.</t>
+          <t>Rin-chan said 'food' to match Miru-chan, then
+promptly sat down at the table.</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1951,8 +1953,8 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>I called again from the hallway while taking the bread
-out of the toaster.</t>
+          <t>I called again from the hallway while taking the
+bread out of the toaster.</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -1967,8 +1969,8 @@
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>I put the bread on the table, then prepared butter and
-strawberry jam.</t>
+          <t>I put the bread on the table, then prepared butter
+and strawberry jam.</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -2441,8 +2443,9 @@
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>While Rurichiyo-chan gave an awkward, forced smile and
-trailed off, Nono-chan beside her looked downcast.</t>
+          <t>While Rurichiyo-chan gave an awkward, forced smile
+and trailed off, Nono-chan beside her looked
+downcast.</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -2518,8 +2521,8 @@
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>I said that and smiled back, but something occurred to
-me.</t>
+          <t>I said that and smiled back, but something occurred
+to me.</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2534,8 +2537,8 @@
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>Maybe, like at bedtime, she needs some kind of routine
-to wake up properly？</t>
+          <t>Maybe, like at bedtime, she needs some kind of
+routine to wake up properly？</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -2597,8 +2600,9 @@
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>Her expressions and speech are composed, and Rin-chan,
-who came earlier, actually looks much sleepier.</t>
+          <t>Her expressions and speech are composed, and
+Rin-chan, who came earlier, actually looks much
+sleepier.</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2705,8 +2709,8 @@
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>She seems plain at first, but she's surprisingly a big
-eater.</t>
+          <t>She seems plain at first, but she's surprisingly a
+big eater.</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -3231,8 +3235,8 @@
       </c>
       <c r="B179" s="1" t="inlineStr">
         <is>
-          <t>Then I held up the electric toothbrush with the switch
-still on to show her.</t>
+          <t>Then I held up the electric toothbrush with the
+switch still on to show her.</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -3599,8 +3603,8 @@
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t>After finishing the house chores, it's time to get the
-bus ready.</t>
+          <t>After finishing the house chores, it's time to get
+the bus ready.</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -3631,8 +3635,8 @@
       </c>
       <c r="B205" s="1" t="inlineStr">
         <is>
-          <t>When I'm driving I'm responsible for everyone's lives,
-so the morning checks are indispensable.</t>
+          <t>When I'm driving I'm responsible for everyone's
+lives, so the morning checks are indispensable.</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -3678,9 +3682,9 @@
       </c>
       <c r="B208" s="1" t="inlineStr">
         <is>
-          <t>It's because everyone likes it, but since it sometimes
-turns into a playground, I can't skip cleaning the
-floor.</t>
+          <t>It's because everyone likes it, but since it
+sometimes turns into a playground, I can't skip
+cleaning the floor.</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3969,9 +3973,9 @@
       </c>
       <c r="B227" s="1" t="inlineStr">
         <is>
-          <t>Next, Rurichiyo-chan climbed up and admonished the two
-of them, but her tone was gentle since it happened
-yesterday too.</t>
+          <t>Next, Rurichiyo-chan climbed up and admonished the
+two of them, but her tone was gentle since it
+happened yesterday too.</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -4262,8 +4266,8 @@
       </c>
       <c r="B246" s="1" t="inlineStr">
         <is>
-          <t>A sudden flash hit me, and I reflexively swept my gaze
-around.</t>
+          <t>A sudden flash hit me, and I reflexively swept my
+gaze around.</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -4432,8 +4436,8 @@
       </c>
       <c r="B257" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan, whose skirt had been lifted, growled like a
-cow.</t>
+          <t>Miru-chan, whose skirt had been lifted, growled like
+a cow.</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -4510,8 +4514,8 @@
       </c>
       <c r="B262" s="1" t="inlineStr">
         <is>
-          <t>Then she reached out and took hold of the collar at my
-neck.</t>
+          <t>Then she reached out and took hold of the collar at
+my neck.</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -4602,8 +4606,8 @@
       <c r="B268" s="1" t="inlineStr">
         <is>
           <t>She went out of her way to nag me — maybe she's
-jealous because I glanced at the panty fortune-telling
-again after yesterday.</t>
+jealous because I glanced at the panty
+fortune-telling again after yesterday.</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -5295,7 +5299,8 @@
       </c>
       <c r="B313" s="1" t="inlineStr">
         <is>
-          <t>「Patrolling, you see, was done to keep everyone safe！」</t>
+          <t>「Patrolling, you see, was done to keep everyone
+safe！」</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -5370,8 +5375,9 @@
       </c>
       <c r="B318" s="1" t="inlineStr">
         <is>
-          <t>...If you only listen to the conversation, Nono-chan's
-tone alone sounds strained and stands out.</t>
+          <t>...If you only listen to the conversation,
+Nono-chan's tone alone sounds strained and stands
+out.</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -5386,11 +5392,11 @@
       </c>
       <c r="B319" s="1" t="inlineStr">
         <is>
-          <t>Well, saying something like "I was just out on patrol"
-in the first place is suspicious enough, and putting
-Miru-chan aside, it feels like Rurichiyo-chan is
-nodding along while fully understanding what's going
-on.</t>
+          <t>Well, saying something like "I was just out on
+patrol" in the first place is suspicious enough, and
+putting Miru-chan aside, it feels like Rurichiyo-chan
+is nodding along while fully understanding what's
+going on.</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -5740,8 +5746,8 @@
       <c r="B342" s="1" t="inlineStr">
         <is>
           <t>「Ah...！ N-no！ In this case, penalties for
-nonperformance don't take immediate effect, so I think
-Janitor-sensei is 'not guilty'！！」</t>
+nonperformance don't take immediate effect, so I
+think Janitor-sensei is 'not guilty'！！」</t>
         </is>
       </c>
       <c r="C342" t="n">
@@ -5756,8 +5762,8 @@
       </c>
       <c r="B343" s="1" t="inlineStr">
         <is>
-          <t>...............She's saying something complicated, but
-her face is completely frazzled.</t>
+          <t>...............She's saying something complicated,
+but her face is completely frazzled.</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -5772,8 +5778,8 @@
       </c>
       <c r="B344" s="1" t="inlineStr">
         <is>
-          <t>That gap makes her panic obvious, but I can still tell
-she's trying to cover for me.</t>
+          <t>That gap makes her panic obvious, but I can still
+tell she's trying to cover for me.</t>
         </is>
       </c>
       <c r="C344" t="n">
@@ -5928,8 +5934,8 @@
       <c r="B354" s="1" t="inlineStr">
         <is>
           <t>It seems totally obvious to the two of them, but it’s
-kind of sweet that neither Rin-chan nor Rurichiyo-chan
-press the matter further…</t>
+kind of sweet that neither Rin-chan nor
+Rurichiyo-chan press the matter further…</t>
         </is>
       </c>
       <c r="C354" t="n">
@@ -6038,8 +6044,8 @@
       </c>
       <c r="B361" s="1" t="inlineStr">
         <is>
-          <t>I thought so, but I could see Rin-chan’s face was beet
-red through the mirror.</t>
+          <t>I thought so, but I could see Rin-chan’s face was
+beet red through the mirror.</t>
         </is>
       </c>
       <c r="C361" t="n">
@@ -6054,9 +6060,9 @@
       </c>
       <c r="B362" s="1" t="inlineStr">
         <is>
-          <t>For the record, I'm staring outside with a sullen look
-like I don't care, but the other girls' chatter goes
-on.</t>
+          <t>For the record, I'm staring outside with a sullen
+look like I don't care, but the other girls' chatter
+goes on.</t>
         </is>
       </c>
       <c r="C362" t="n">
@@ -6117,7 +6123,8 @@
       </c>
       <c r="B366" s="1" t="inlineStr">
         <is>
-          <t>「Oh? Is that so? I thought you belonged to Nono-chan.」</t>
+          <t>「Oh? Is that so? I thought you belonged to
+Nono-chan.」</t>
         </is>
       </c>
       <c r="C366" t="n">
@@ -6301,8 +6308,8 @@
       </c>
       <c r="B378" s="1" t="inlineStr">
         <is>
-          <t>「No, no！ Aren't you actually the one who came to visit
-Rin-chan？」</t>
+          <t>「No, no！ Aren't you actually the one who came to
+visit Rin-chan？」</t>
         </is>
       </c>
       <c r="C378" t="n">
@@ -6744,9 +6751,9 @@
       </c>
       <c r="B407" s="1" t="inlineStr">
         <is>
-          <t>Rin, turning back in a desperate huff, kept her cheeks
-bright red, puffed them up, and stuck out her lips in
-a pout.</t>
+          <t>Rin, turning back in a desperate huff, kept her
+cheeks bright red, puffed them up, and stuck out her
+lips in a pout.</t>
         </is>
       </c>
       <c r="C407" t="n">
@@ -7221,7 +7228,8 @@
       </c>
       <c r="B438" s="1" t="inlineStr">
         <is>
-          <t>I can see everyone looking puzzled through the mirror.</t>
+          <t>I can see everyone looking puzzled through the
+mirror.</t>
         </is>
       </c>
       <c r="C438" t="n">
@@ -7236,9 +7244,9 @@
       </c>
       <c r="B439" s="1" t="inlineStr">
         <is>
-          <t>It was only Miru-chan's place that I actually went to,
-but since Miru-chan was asleep the whole time, it's no
-wonder she doesn't remember at all.</t>
+          <t>It was only Miru-chan's place that I actually went
+to, but since Miru-chan was asleep the whole time,
+it's no wonder she doesn't remember at all.</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -7299,7 +7307,8 @@
       </c>
       <c r="B443" s="1" t="inlineStr">
         <is>
-          <t>I can see everyone looking puzzled through the mirror.</t>
+          <t>I can see everyone looking puzzled through the
+mirror.</t>
         </is>
       </c>
       <c r="C443" t="n">
@@ -7330,8 +7339,8 @@
       </c>
       <c r="B445" s="1" t="inlineStr">
         <is>
-          <t>I guess it means I was half-asleep the whole time last
-night after all......</t>
+          <t>I guess it means I was half-asleep the whole time
+last night after all......</t>
         </is>
       </c>
       <c r="C445" t="n">
@@ -7346,8 +7355,8 @@
       </c>
       <c r="B446" s="1" t="inlineStr">
         <is>
-          <t>But because of that, there's this vibe that nobody has
-any idea who it could have been.</t>
+          <t>But because of that, there's this vibe that nobody
+has any idea who it could have been.</t>
         </is>
       </c>
       <c r="C446" t="n">
@@ -7593,8 +7602,8 @@
       </c>
       <c r="B462" s="1" t="inlineStr">
         <is>
-          <t>Thanks to kind-hearted Rurichiyo-chan covering for me,
-things seem to be calming down.</t>
+          <t>Thanks to kind-hearted Rurichiyo-chan covering for
+me, things seem to be calming down.</t>
         </is>
       </c>
       <c r="C462" t="n">
@@ -7807,8 +7816,8 @@
       </c>
       <c r="B476" s="1" t="inlineStr">
         <is>
-          <t>「Okay, I think it's kind of suspicious you went out of
-your way to be awake.」</t>
+          <t>「Okay, I think it's kind of suspicious you went out
+of your way to be awake.」</t>
         </is>
       </c>
       <c r="C476" t="n">
@@ -8055,9 +8064,9 @@
       </c>
       <c r="B492" s="1" t="inlineStr">
         <is>
-          <t>Damn... I relaxed because it seemed last night's thing
-hadn't been found out, so I let my guard down and
-joked, and that made things worse.</t>
+          <t>Damn... I relaxed because it seemed last night's
+thing hadn't been found out, so I let my guard down
+and joked, and that made things worse.</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -8752,8 +8761,8 @@
       </c>
       <c r="B537" s="1" t="inlineStr">
         <is>
-          <t>If anything happens, I'll just have to deal with it as
-it comes.</t>
+          <t>If anything happens, I'll just have to deal with it
+as it comes.</t>
         </is>
       </c>
       <c r="C537" t="n">
@@ -8860,8 +8869,8 @@
       </c>
       <c r="B544" s="1" t="inlineStr">
         <is>
-          <t>I couldn't say I was thinking about how to support the
-lesson because that would impinge on Nono-chan's
+          <t>I couldn't say I was thinking about how to support
+the lesson because that would impinge on Nono-chan's
 pride.</t>
         </is>
       </c>
@@ -8954,8 +8963,8 @@
       </c>
       <c r="B550" s="1" t="inlineStr">
         <is>
-          <t>...Rurichiyo-chan is kind, but right now that innocent
-bluntness of hers is painful.</t>
+          <t>...Rurichiyo-chan is kind, but right now that
+innocent bluntness of hers is painful.</t>
         </is>
       </c>
       <c r="C550" t="n">
@@ -9062,8 +9071,8 @@
       </c>
       <c r="B557" s="1" t="inlineStr">
         <is>
-          <t>I can't tell if she's really depending on me or not...
-.</t>
+          <t>I can't tell if she's really depending on me or
+not... .</t>
         </is>
       </c>
       <c r="C557" t="n">
@@ -9305,8 +9314,8 @@
       </c>
       <c r="B573" s="1" t="inlineStr">
         <is>
-          <t>The image 'physical exam equals naked' flashed through
-my head.</t>
+          <t>The image 'physical exam equals naked' flashed
+through my head.</t>
         </is>
       </c>
       <c r="C573" t="n">
@@ -9397,8 +9406,8 @@
       </c>
       <c r="B579" s="1" t="inlineStr">
         <is>
-          <t>I blurted the words back in a panic, but maybe I chose
-the wrong ones... .</t>
+          <t>I blurted the words back in a panic, but maybe I
+chose the wrong ones... .</t>
         </is>
       </c>
       <c r="C579" t="n">
@@ -9565,9 +9574,9 @@
       </c>
       <c r="B590" s="1" t="inlineStr">
         <is>
-          <t>On the other hand, Rin-chan, as if she could see right
-through my thoughts, glares at me with a flushed face
-and that sullen, half-lidded stare.</t>
+          <t>On the other hand, Rin-chan, as if she could see
+right through my thoughts, glares at me with a
+flushed face and that sullen, half-lidded stare.</t>
         </is>
       </c>
       <c r="C590" t="n">
@@ -9886,8 +9895,8 @@
       </c>
       <c r="B611" s="1" t="inlineStr">
         <is>
-          <t>「Um…！ No, like Rin-chan said, I think it’s better if I
-go outside！」</t>
+          <t>「Um…！ No, like Rin-chan said, I think it’s better if
+I go outside！」</t>
         </is>
       </c>
       <c r="C611" t="n">
@@ -9902,8 +9911,8 @@
       </c>
       <c r="B612" s="1" t="inlineStr">
         <is>
-          <t>Feeling sorry for Rin-chan, I instinctively thought to
-defend her.</t>
+          <t>Feeling sorry for Rin-chan, I instinctively thought
+to defend her.</t>
         </is>
       </c>
       <c r="C612" t="n">
@@ -10610,8 +10619,8 @@
       </c>
       <c r="B658" s="1" t="inlineStr">
         <is>
-          <t>Keeping as far away from the classrooms as possible, I
-wandered around inside and outside the school
+          <t>Keeping as far away from the classrooms as possible,
+I wandered around inside and outside the school
 building.</t>
         </is>
       </c>
@@ -10814,8 +10823,8 @@
       </c>
       <c r="B671" s="1" t="inlineStr">
         <is>
-          <t>Uuu... Even if I can't enter the Assembly Hall, I want
-to at least savor the air.</t>
+          <t>Uuu... Even if I can't enter the Assembly Hall, I
+want to at least savor the air.</t>
         </is>
       </c>
       <c r="C671" t="n">
@@ -10875,8 +10884,8 @@
       </c>
       <c r="B675" s="1" t="inlineStr">
         <is>
-          <t>A few seconds of silence followed after Nono-chan said
-that.</t>
+          <t>A few seconds of silence followed after Nono-chan
+said that.</t>
         </is>
       </c>
       <c r="C675" t="n">
@@ -10937,7 +10946,8 @@
       <c r="B679" s="1" t="inlineStr">
         <is>
           <t>Did Nono-chan wrap the measuring tape too tight and
-end up rubbing it against Miru-chan's chest, I wonder？</t>
+end up rubbing it against Miru-chan's chest, I
+wonder？</t>
         </is>
       </c>
       <c r="C679" t="n">
@@ -11631,8 +11641,8 @@
       </c>
       <c r="B725" s="1" t="inlineStr">
         <is>
-          <t>...How should I put it, just as I expected they're all
-flustered.</t>
+          <t>...How should I put it, just as I expected they're
+all flustered.</t>
         </is>
       </c>
       <c r="C725" t="n">
@@ -11863,8 +11873,8 @@
       </c>
       <c r="B740" s="1" t="inlineStr">
         <is>
-          <t>Everyone is bare-chested in just their underwear, each
-holding a body-measurement sheet.</t>
+          <t>Everyone is bare-chested in just their underwear,
+each holding a body-measurement sheet.</t>
         </is>
       </c>
       <c r="C740" t="n">
@@ -12489,8 +12499,8 @@
       </c>
       <c r="B781" s="1" t="inlineStr">
         <is>
-          <t>Hmm, yeah, I think a 2-millimeter difference is within
-the margin of error too.</t>
+          <t>Hmm, yeah, I think a 2-millimeter difference is
+within the margin of error too.</t>
         </is>
       </c>
       <c r="C781" t="n">
@@ -12581,8 +12591,8 @@
       </c>
       <c r="B787" s="1" t="inlineStr">
         <is>
-          <t>「Hmph... It's the same no matter how many times you do
-it...」</t>
+          <t>「Hmph... It's the same no matter how many times you
+do it...」</t>
         </is>
       </c>
       <c r="C787" t="n">
@@ -12614,8 +12624,8 @@
       <c r="B789" s="1" t="inlineStr">
         <is>
           <t>She's probably aware that, within about a
-two-millimeter margin of error, it could go either way
-this time.</t>
+two-millimeter margin of error, it could go either
+way this time.</t>
         </is>
       </c>
       <c r="C789" t="n">
@@ -12660,8 +12670,8 @@
       </c>
       <c r="B792" s="1" t="inlineStr">
         <is>
-          <t>And for some reason Rurichiyo-chan is also eager for a
-re-measurement….</t>
+          <t>And for some reason Rurichiyo-chan is also eager for
+a re-measurement….</t>
         </is>
       </c>
       <c r="C792" t="n">
@@ -12968,8 +12978,8 @@
       </c>
       <c r="B812" s="1" t="inlineStr">
         <is>
-          <t>「Now that you mention it, I feel like that happened to
-me too！」</t>
+          <t>「Now that you mention it, I feel like that happened
+to me too！」</t>
         </is>
       </c>
       <c r="C812" t="n">
@@ -12984,8 +12994,8 @@
       </c>
       <c r="B813" s="1" t="inlineStr">
         <is>
-          <t>I don't remember that happening to Rurichiyo-chan, but
-since I wasn't watching I can't say for sure.</t>
+          <t>I don't remember that happening to Rurichiyo-chan,
+but since I wasn't watching I can't say for sure.</t>
         </is>
       </c>
       <c r="C813" t="n">
@@ -13382,8 +13392,8 @@
       </c>
       <c r="B839" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan agrees with Miru-chan while encouraging
-Nono-chan.</t>
+          <t>Rurichiyo-chan agrees with Miru-chan while
+encouraging Nono-chan.</t>
         </is>
       </c>
       <c r="C839" t="n">
@@ -13625,9 +13635,9 @@
       </c>
       <c r="B855" s="1" t="inlineStr">
         <is>
-          <t>I pressed my back against the wall and held my breath,
-and the door right next to me swung open with a
-noise—！</t>
+          <t>I pressed my back against the wall and held my
+breath, and the door right next to me swung open with
+a noise—！</t>
         </is>
       </c>
       <c r="C855" t="n">
@@ -13903,9 +13913,9 @@
       </c>
       <c r="B873" s="1" t="inlineStr">
         <is>
-          <t>With the get-out-of-refusal-free card of 'if Nono-chan
-asks I can't say no,' I stepped into the assembly
-hall.</t>
+          <t>With the get-out-of-refusal-free card of 'if
+Nono-chan asks I can't say no,' I stepped into the
+assembly hall.</t>
         </is>
       </c>
       <c r="C873" t="n">
@@ -13951,8 +13961,8 @@
       </c>
       <c r="B876" s="1" t="inlineStr">
         <is>
-          <t>「M-m, everyone, Janitor-sensei is going to measure how
-scared you all are！」</t>
+          <t>「M-m, everyone, Janitor-sensei is going to measure
+how scared you all are！」</t>
         </is>
       </c>
       <c r="C876" t="n">
@@ -14073,8 +14083,8 @@
       </c>
       <c r="B884" s="1" t="inlineStr">
         <is>
-          <t>Of course everyone was bewildered, since I had come in
-during the physical measurements.</t>
+          <t>Of course everyone was bewildered, since I had come
+in during the physical measurements.</t>
         </is>
       </c>
       <c r="C884" t="n">
@@ -14779,8 +14789,8 @@
       <c r="B930" s="1" t="inlineStr">
         <is>
           <t>Hmm, I don't really have confidence I'll do it well
-either, but if Nono-chan's counting on me, I've got no
-choice but to go for it.</t>
+either, but if Nono-chan's counting on me, I've got
+no choice but to go for it.</t>
         </is>
       </c>
       <c r="C930" t="n">
@@ -14948,8 +14958,8 @@
       <c r="B941" s="1" t="inlineStr">
         <is>
           <t>「Right. I mean, Nono-chan-sensei is already using a
-tape measure, so I thought it might be better to try a
-different method.」</t>
+tape measure, so I thought it might be better to try
+a different method.」</t>
         </is>
       </c>
       <c r="C941" t="n">
@@ -15009,7 +15019,8 @@
       </c>
       <c r="B945" s="1" t="inlineStr">
         <is>
-          <t>She must have sensed what was going to be done to her.</t>
+          <t>She must have sensed what was going to be done to
+her.</t>
         </is>
       </c>
       <c r="C945" t="n">
@@ -15254,7 +15265,8 @@
       <c r="B961" s="1" t="inlineStr">
         <is>
           <t>「In this case medical practice would fit—it's because
-human hands are superior for touching and diagnosing！」</t>
+human hands are superior for touching and
+diagnosing！」</t>
         </is>
       </c>
       <c r="C961" t="n">
@@ -15816,8 +15828,8 @@
       </c>
       <c r="B998" s="1" t="inlineStr">
         <is>
-          <t>Even though that distance felt endlessly far, before I
-knew it my hand was touching Miru-chan's chest.</t>
+          <t>Even though that distance felt endlessly far, before
+I knew it my hand was touching Miru-chan's chest.</t>
         </is>
       </c>
       <c r="C998" t="n">
@@ -15862,8 +15874,8 @@
       </c>
       <c r="B1001" s="1" t="inlineStr">
         <is>
-          <t>The moment my hand touched her chest, Miru-chan gave a
-little jolt and let out a small breath.</t>
+          <t>The moment my hand touched her chest, Miru-chan gave
+a little jolt and let out a small breath.</t>
         </is>
       </c>
       <c r="C1001" t="n">
@@ -16200,8 +16212,8 @@
       </c>
       <c r="B1023" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan has no way of knowing what I'm thinking; she
-just stays still and endures.</t>
+          <t>Miru-chan has no way of knowing what I'm thinking;
+she just stays still and endures.</t>
         </is>
       </c>
       <c r="C1023" t="n">
@@ -16310,8 +16322,8 @@
         <is>
           <t>I refocus my attention on the shape of my hand and,
 with movements like a precision machine, I let it
-follow the gentle swell and make sure each finger fits
-the soft skin.</t>
+follow the gentle swell and make sure each finger
+fits the soft skin.</t>
         </is>
       </c>
       <c r="C1030" t="n">
@@ -16326,8 +16338,8 @@
       </c>
       <c r="B1031" s="1" t="inlineStr">
         <is>
-          <t>If I press too hard the skin will dent, so gentle like
-when stroking, but with a sure intent...！</t>
+          <t>If I press too hard the skin will dent, so gentle
+like when stroking, but with a sure intent...！</t>
         </is>
       </c>
       <c r="C1031" t="n">
@@ -16481,7 +16493,8 @@
       </c>
       <c r="B1041" s="1" t="inlineStr">
         <is>
-          <t>I hid my happiness in my heart and called out to them.</t>
+          <t>I hid my happiness in my heart and called out to
+them.</t>
         </is>
       </c>
       <c r="C1041" t="n">
@@ -16693,8 +16706,8 @@
       </c>
       <c r="B1055" s="1" t="inlineStr">
         <is>
-          <t>When I pointed my hands, still frozen, Rin-chan sucked
-in a breath.</t>
+          <t>When I pointed my hands, still frozen, Rin-chan
+sucked in a breath.</t>
         </is>
       </c>
       <c r="C1055" t="n">
@@ -17077,8 +17090,8 @@
       </c>
       <c r="B1080" s="1" t="inlineStr">
         <is>
-          <t>When it was Miru-chan, her reaction was so cute that I
-got distracted by it, and I regret that.</t>
+          <t>When it was Miru-chan, her reaction was so cute that
+I got distracted by it, and I regret that.</t>
         </is>
       </c>
       <c r="C1080" t="n">
@@ -17200,8 +17213,8 @@
       </c>
       <c r="B1088" s="1" t="inlineStr">
         <is>
-          <t>If I took too long, Rin-chan’s held-back embarrassment
-might explode.</t>
+          <t>If I took too long, Rin-chan’s held-back
+embarrassment might explode.</t>
         </is>
       </c>
       <c r="C1088" t="n">
@@ -17216,8 +17229,8 @@
       </c>
       <c r="B1089" s="1" t="inlineStr">
         <is>
-          <t>With that thought, I focused my attention on the palms
-of my hands more than ever.</t>
+          <t>With that thought, I focused my attention on the
+palms of my hands more than ever.</t>
         </is>
       </c>
       <c r="C1089" t="n">
@@ -17232,8 +17245,8 @@
       </c>
       <c r="B1090" s="1" t="inlineStr">
         <is>
-          <t>In my head I was a phantom thief cracking a dial-style
-safe.</t>
+          <t>In my head I was a phantom thief cracking a
+dial-style safe.</t>
         </is>
       </c>
       <c r="C1090" t="n">
@@ -17723,8 +17736,8 @@
       </c>
       <c r="B1122" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan came in front of me with a serious face
-and snapped to attention on her own.</t>
+          <t>Rurichiyo-chan came in front of me with a serious
+face and snapped to attention on her own.</t>
         </is>
       </c>
       <c r="C1122" t="n">
@@ -17755,8 +17768,8 @@
       </c>
       <c r="B1124" s="1" t="inlineStr">
         <is>
-          <t>I felt like I shouldn't ask, but I also wanted to know
-the numbers Nono-chan measured...</t>
+          <t>I felt like I shouldn't ask, but I also wanted to
+know the numbers Nono-chan measured...</t>
         </is>
       </c>
       <c r="C1124" t="n">
@@ -18200,8 +18213,8 @@
       </c>
       <c r="B1153" s="1" t="inlineStr">
         <is>
-          <t>Because it's Rurichiyo-chan, would she feel a sense of
-motherhood before feeling anything sexual when her
+          <t>Because it's Rurichiyo-chan, would she feel a sense
+of motherhood before feeling anything sexual when her
 chest is touched？</t>
         </is>
       </c>
@@ -19370,8 +19383,8 @@
       </c>
       <c r="B1229" s="1" t="inlineStr">
         <is>
-          <t>When I looked up at the call, Nono-chan was looking at
-me with a puzzled expression.</t>
+          <t>When I looked up at the call, Nono-chan was looking
+at me with a puzzled expression.</t>
         </is>
       </c>
       <c r="C1229" t="n">
@@ -19720,7 +19733,8 @@
       </c>
       <c r="B1252" s="1" t="inlineStr">
         <is>
-          <t>Every time my fingers slipped, Nono-chan's voice rose.</t>
+          <t>Every time my fingers slipped, Nono-chan's voice
+rose.</t>
         </is>
       </c>
       <c r="C1252" t="n">
@@ -19812,8 +19826,8 @@
       </c>
       <c r="B1258" s="1" t="inlineStr">
         <is>
-          <t>Maybe my fingers felt that too, because they naturally
-warmed up.</t>
+          <t>Maybe my fingers felt that too, because they
+naturally warmed up.</t>
         </is>
       </c>
       <c r="C1258" t="n">
@@ -20088,7 +20102,8 @@
       </c>
       <c r="B1276" s="1" t="inlineStr">
         <is>
-          <t>No, my fingers were probably visibly trembling by now.</t>
+          <t>No, my fingers were probably visibly trembling by
+now.</t>
         </is>
       </c>
       <c r="C1276" t="n">
@@ -20135,8 +20150,9 @@
       </c>
       <c r="B1279" s="1" t="inlineStr">
         <is>
-          <t>Thinking I was at my limit in every sense, I tightened
-my open fingers and let go, keeping that shape.</t>
+          <t>Thinking I was at my limit in every sense, I
+tightened my open fingers and let go, keeping that
+shape.</t>
         </is>
       </c>
       <c r="C1279" t="n">
@@ -20456,8 +20472,8 @@
       </c>
       <c r="B1300" s="1" t="inlineStr">
         <is>
-          <t>...Or rather, everyone's chests were so wonderful that
-I couldn't possibly compare them...！</t>
+          <t>...Or rather, everyone's chests were so wonderful
+that I couldn't possibly compare them...！</t>
         </is>
       </c>
       <c r="C1300" t="n">
@@ -20607,8 +20623,8 @@
       </c>
       <c r="B1310" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan keeps her head down and mumbles, putting on a
-brave face.</t>
+          <t>Rin-chan keeps her head down and mumbles, putting on
+a brave face.</t>
         </is>
       </c>
       <c r="C1310" t="n">
@@ -20930,9 +20946,9 @@
       </c>
       <c r="B1331" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan, Rurichiyo-chan, and Nono-chan each seemed to
-feel it in their own ways, but when it comes to this,
-Miru-chan is hands down the best…！</t>
+          <t>Rin-chan, Rurichiyo-chan, and Nono-chan each seemed
+to feel it in their own ways, but when it comes to
+this, Miru-chan is hands down the best…！</t>
         </is>
       </c>
       <c r="C1331" t="n">
@@ -21282,9 +21298,9 @@
       </c>
       <c r="B1354" s="1" t="inlineStr">
         <is>
-          <t>When the results came out, Rurichiyo-chan, who readily
-accepts them and doesn't fuss, offered words of
-praise.</t>
+          <t>When the results came out, Rurichiyo-chan, who
+readily accepts them and doesn't fuss, offered words
+of praise.</t>
         </is>
       </c>
       <c r="C1354" t="n">
@@ -21705,8 +21721,8 @@
       </c>
       <c r="B1382" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan, whose name was deliberately said wrong, got
-past being angry and instead smiled.</t>
+          <t>Miru-chan, whose name was deliberately said wrong,
+got past being angry and instead smiled.</t>
         </is>
       </c>
       <c r="C1382" t="n">
@@ -22501,8 +22517,8 @@
       <c r="B1434" s="1" t="inlineStr">
         <is>
           <t>My fingers got tired and I sometimes ended up being
-rougher than with the others, but the one who gave the
-best reaction was Nono-chan.</t>
+rougher than with the others, but the one who gave
+the best reaction was Nono-chan.</t>
         </is>
       </c>
       <c r="C1434" t="n">
@@ -22685,8 +22701,8 @@
       </c>
       <c r="B1446" s="1" t="inlineStr">
         <is>
-          <t>Still, everyone's celebrating like it's their own good
-fortune.</t>
+          <t>Still, everyone's celebrating like it's their own
+good fortune.</t>
         </is>
       </c>
       <c r="C1446" t="n">
@@ -22765,8 +22781,9 @@
       </c>
       <c r="B1451" s="1" t="inlineStr">
         <is>
-          <t>Well, after that everyone snapped back to their senses
-and kicked me out, but it was more than enough.</t>
+          <t>Well, after that everyone snapped back to their
+senses and kicked me out, but it was more than
+enough.</t>
         </is>
       </c>
       <c r="C1451" t="n">
@@ -23135,8 +23152,9 @@
       </c>
       <c r="B1475" s="1" t="inlineStr">
         <is>
-          <t>The plump flesh pushes the fabric up, and on the other
-hand the deep creases it makes are irresistible.</t>
+          <t>The plump flesh pushes the fabric up, and on the
+other hand the deep creases it makes are
+irresistible.</t>
         </is>
       </c>
       <c r="C1475" t="n">
@@ -23214,8 +23232,8 @@
       <c r="B1480" s="1" t="inlineStr">
         <is>
           <t>Staring at my crotch with deep feeling, Rin-chan
-reached out her arm and poked and rubbed my cheek with
-her fist.</t>
+reached out her arm and poked and rubbed my cheek
+with her fist.</t>
         </is>
       </c>
       <c r="C1480" t="n">
@@ -23260,8 +23278,8 @@
       </c>
       <c r="B1483" s="1" t="inlineStr">
         <is>
-          <t>Maybe egged on by Rin-chan, Miru-chan wraps both hands
-around my arm and gives it playful little pats.</t>
+          <t>Maybe egged on by Rin-chan, Miru-chan wraps both
+hands around my arm and gives it playful little pats.</t>
         </is>
       </c>
       <c r="C1483" t="n">
@@ -23383,8 +23401,8 @@
       <c r="B1491" s="1" t="inlineStr">
         <is>
           <t>My cheek gets rubbed and my arm gets playfully
-slapped... losing my footing, I forcefully changed the
-subject.</t>
+slapped... losing my footing, I forcefully changed
+the subject.</t>
         </is>
       </c>
       <c r="C1491" t="n">
@@ -23414,8 +23432,8 @@
       </c>
       <c r="B1493" s="1" t="inlineStr">
         <is>
-          <t>「Nono-chan... sensei said I'd change in the staff room
-and then come.」</t>
+          <t>「Nono-chan... sensei said I'd change in the staff
+room and then come.」</t>
         </is>
       </c>
       <c r="C1493" t="n">
@@ -23581,8 +23599,8 @@
       </c>
       <c r="B1504" s="1" t="inlineStr">
         <is>
-          <t>They say speak of the devil, and sure enough Nono-chan
-came out of the school building...</t>
+          <t>They say speak of the devil, and sure enough
+Nono-chan came out of the school building...</t>
         </is>
       </c>
       <c r="C1504" t="n">
@@ -23612,8 +23630,8 @@
       </c>
       <c r="B1506" s="1" t="inlineStr">
         <is>
-          <t>Like the others, Nono-chan was wearing the gym uniform
-with the Youjou Academy crest on the chest.</t>
+          <t>Like the others, Nono-chan was wearing the gym
+uniform with the Youjou Academy crest on the chest.</t>
         </is>
       </c>
       <c r="C1506" t="n">
@@ -23733,8 +23751,8 @@
       </c>
       <c r="B1514" s="1" t="inlineStr">
         <is>
-          <t>Sudden as it is, the main point has got to be the edge
-where skin meets fabric！</t>
+          <t>Sudden as it is, the main point has got to be the
+edge where skin meets fabric！</t>
         </is>
       </c>
       <c r="C1514" t="n">
@@ -23797,8 +23815,8 @@
       </c>
       <c r="B1518" s="1" t="inlineStr">
         <is>
-          <t>Because it's not underwear, it actually makes the skin
-stand out...！</t>
+          <t>Because it's not underwear, it actually makes the
+skin stand out...！</t>
         </is>
       </c>
       <c r="C1518" t="n">
@@ -24013,9 +24031,9 @@
       </c>
       <c r="B1532" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan, who had just come out to the schoolyard and
-didn't understand the situation, rounded her eyes when
-she saw us.</t>
+          <t>Nono-chan, who had just come out to the schoolyard
+and didn't understand the situation, rounded her eyes
+when she saw us.</t>
         </is>
       </c>
       <c r="C1532" t="n">
@@ -24045,7 +24063,8 @@
       </c>
       <c r="B1534" s="1" t="inlineStr">
         <is>
-          <t>「Niini was looking at Nono-chan sensei with lewd eyes」</t>
+          <t>「Niini was looking at Nono-chan sensei with lewd
+eyes」</t>
         </is>
       </c>
       <c r="C1534" t="n">
@@ -24493,8 +24512,8 @@
       <c r="B1563" s="1" t="inlineStr">
         <is>
           <t>She's likely feeling a bit more smug than usual
-because it's her mom's thing, but it's unusual for her
-to brandish that around.</t>
+because it's her mom's thing, but it's unusual for
+her to brandish that around.</t>
         </is>
       </c>
       <c r="C1563" t="n">
@@ -24678,7 +24697,8 @@
       </c>
       <c r="B1575" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan makes a look of shock I've never seen before.</t>
+          <t>Rin-chan makes a look of shock I've never seen
+before.</t>
         </is>
       </c>
       <c r="C1575" t="n">
@@ -24927,8 +24947,8 @@
       </c>
       <c r="B1591" s="1" t="inlineStr">
         <is>
-          <t>The closing ceremony's coming up soon, and if it's PE,
-I guess that's about what you'd expect.</t>
+          <t>The closing ceremony's coming up soon, and if it's
+PE, I guess that's about what you'd expect.</t>
         </is>
       </c>
       <c r="C1591" t="n">
@@ -25109,8 +25129,8 @@
       </c>
       <c r="B1603" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan gives a hesitant sort of yes, ending up
-with a light, embarrassed smile.</t>
+          <t>Rurichiyo-chan gives a hesitant sort of yes, ending
+up with a light, embarrassed smile.</t>
         </is>
       </c>
       <c r="C1603" t="n">
@@ -25396,8 +25416,8 @@
       </c>
       <c r="B1622" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan and Rurichiyo-chan were more like I had them
-cling on while I supported them, though.</t>
+          <t>Nono-chan and Rurichiyo-chan were more like I had
+them cling on while I supported them, though.</t>
         </is>
       </c>
       <c r="C1622" t="n">
@@ -25503,8 +25523,8 @@
       </c>
       <c r="B1629" s="1" t="inlineStr">
         <is>
-          <t>「If it gets too hard, ease up！ If you come down little
-by little, I'll catch you！」</t>
+          <t>「If it gets too hard, ease up！ If you come down
+little by little, I'll catch you！」</t>
         </is>
       </c>
       <c r="C1629" t="n">
@@ -25534,8 +25554,8 @@
       </c>
       <c r="B1631" s="1" t="inlineStr">
         <is>
-          <t>If it happens to fall, I'll put my body on the line to
-protect it.</t>
+          <t>If it happens to fall, I'll put my body on the line
+to protect it.</t>
         </is>
       </c>
       <c r="C1631" t="n">
@@ -25580,8 +25600,8 @@
       </c>
       <c r="B1634" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan is the only one calmly enjoying the climbing
-pole by herself.</t>
+          <t>Miru-chan is the only one calmly enjoying the
+climbing pole by herself.</t>
         </is>
       </c>
       <c r="C1634" t="n">
@@ -25596,8 +25616,8 @@
       </c>
       <c r="B1635" s="1" t="inlineStr">
         <is>
-          <t>She might be bad at handstands, but she's clearly good
-at the climbing pole.</t>
+          <t>She might be bad at handstands, but she's clearly
+good at the climbing pole.</t>
         </is>
       </c>
       <c r="C1635" t="n">
@@ -25659,8 +25679,8 @@
       <c r="B1639" s="1" t="inlineStr">
         <is>
           <t>「If I support myself with my arms and bend and
-straighten my spine... I should be able to go up using
-a bending-and-straightening motion...！」</t>
+straighten my spine... I should be able to go up
+using a bending-and-straightening motion...！」</t>
         </is>
       </c>
       <c r="C1639" t="n">
@@ -25971,8 +25991,8 @@
       </c>
       <c r="B1659" s="1" t="inlineStr">
         <is>
-          <t>Meanwhile, Rurichiyo-chan is clinging on and is on the
-verge of giving up.</t>
+          <t>Meanwhile, Rurichiyo-chan is clinging on and is on
+the verge of giving up.</t>
         </is>
       </c>
       <c r="C1659" t="n">
@@ -26495,8 +26515,8 @@
       </c>
       <c r="B1693" s="1" t="inlineStr">
         <is>
-          <t>Her curvy lower body winds around the rod and wriggles
-restlessly.</t>
+          <t>Her curvy lower body winds around the rod and
+wriggles restlessly.</t>
         </is>
       </c>
       <c r="C1693" t="n">
@@ -26542,8 +26562,8 @@
       </c>
       <c r="B1696" s="1" t="inlineStr">
         <is>
-          <t>「Nn, nngh...！ I-I think I'm starting to get it, just a
-little！」</t>
+          <t>「Nn, nngh...！ I-I think I'm starting to get it, just
+a little！」</t>
         </is>
       </c>
       <c r="C1696" t="n">
@@ -26589,8 +26609,8 @@
       </c>
       <c r="B1699" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan pressed her crotch firmly against the stick,
-trying to balance herself with a grunt.</t>
+          <t>Nono-chan pressed her crotch firmly against the
+stick, trying to balance herself with a grunt.</t>
         </is>
       </c>
       <c r="C1699" t="n">
@@ -26605,8 +26625,8 @@
       </c>
       <c r="B1700" s="1" t="inlineStr">
         <is>
-          <t>Maybe because of that posture, a little of her panties
-were peeking out of the bloomers...</t>
+          <t>Maybe because of that posture, a little of her
+panties were peeking out of the bloomers...</t>
         </is>
       </c>
       <c r="C1700" t="n">
@@ -26789,8 +26809,8 @@
       </c>
       <c r="B1712" s="1" t="inlineStr">
         <is>
-          <t>The two of them tightened their bodies more around the
-stick and answered.</t>
+          <t>The two of them tightened their bodies more around
+the stick and answered.</t>
         </is>
       </c>
       <c r="C1712" t="n">
@@ -26945,8 +26965,8 @@
       </c>
       <c r="B1722" s="1" t="inlineStr">
         <is>
-          <t>Relieved, I relaxed, and Rin-chan, without looking up,
-spoke to Miru-chan.</t>
+          <t>Relieved, I relaxed, and Rin-chan, without looking
+up, spoke to Miru-chan.</t>
         </is>
       </c>
       <c r="C1722" t="n">
@@ -27539,8 +27559,8 @@
       <c r="B1761" s="1" t="inlineStr">
         <is>
           <t>If you look, Nono-chan is bending her body into a
-crooked shape and wriggling her lower half to keep her
-balance.</t>
+crooked shape and wriggling her lower half to keep
+her balance.</t>
         </is>
       </c>
       <c r="C1761" t="n">
@@ -27616,8 +27636,8 @@
       </c>
       <c r="B1766" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan is holding herself from sliding down by
-wrapping her crotch around the stick.</t>
+          <t>Rurichiyo-chan is holding herself from sliding down
+by wrapping her crotch around the stick.</t>
         </is>
       </c>
       <c r="C1766" t="n">
@@ -28058,8 +28078,8 @@
       </c>
       <c r="B1795" s="1" t="inlineStr">
         <is>
-          <t>Isn’t this the kind of thing that only happens once in
-a lifetime！？</t>
+          <t>Isn’t this the kind of thing that only happens once
+in a lifetime！？</t>
         </is>
       </c>
       <c r="C1795" t="n">
@@ -28441,7 +28461,8 @@
       </c>
       <c r="B1820" s="1" t="inlineStr">
         <is>
-          <t>Hearing Miru-chan's scream, I spun around reflexively.</t>
+          <t>Hearing Miru-chan's scream, I spun around
+reflexively.</t>
         </is>
       </c>
       <c r="C1820" t="n">
@@ -28625,8 +28646,8 @@
       </c>
       <c r="B1832" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan doesn't seem hurt, so I should probably call
-this a perk！</t>
+          <t>Miru-chan doesn't seem hurt, so I should probably
+call this a perk！</t>
         </is>
       </c>
       <c r="C1832" t="n">
@@ -28980,8 +29001,8 @@
       </c>
       <c r="B1855" s="1" t="inlineStr">
         <is>
-          <t>...I lunged forward, but Rin-chan wasn't there, and my
-face crashed into the Noboribō.</t>
+          <t>...I lunged forward, but Rin-chan wasn't there, and
+my face crashed into the Noboribō.</t>
         </is>
       </c>
       <c r="C1855" t="n">
@@ -29118,9 +29139,9 @@
       </c>
       <c r="B1864" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan, who landed on the ground, looks at me with a
-subtle expression that's part angry and part about to
-cry.</t>
+          <t>Rin-chan, who landed on the ground, looks at me with
+a subtle expression that's part angry and part about
+to cry.</t>
         </is>
       </c>
       <c r="C1864" t="n">
@@ -30190,8 +30211,8 @@
       </c>
       <c r="B1934" s="1" t="inlineStr">
         <is>
-          <t>After being dazed for a while, Nono suddenly sprang to
-her feet.</t>
+          <t>After being dazed for a while, Nono suddenly sprang
+to her feet.</t>
         </is>
       </c>
       <c r="C1934" t="n">
@@ -30620,9 +30641,9 @@
       </c>
       <c r="B1962" s="1" t="inlineStr">
         <is>
-          <t>Whether I'm cooking, driving them to and from the bus,
-cleaning, or helping with class, I get to see them all
-being thrilled or embarrassed.</t>
+          <t>Whether I'm cooking, driving them to and from the
+bus, cleaning, or helping with class, I get to see
+them all being thrilled or embarrassed.</t>
         </is>
       </c>
       <c r="C1962" t="n">
@@ -30638,7 +30659,8 @@
       <c r="B1963" s="1" t="inlineStr">
         <is>
           <t>Ah... to be able to watch the little ones up close
-every day — I'm really living in a lucky situation...！</t>
+every day — I'm really living in a lucky
+situation...！</t>
         </is>
       </c>
       <c r="C1963" t="n">
@@ -30925,7 +30947,8 @@
       </c>
       <c r="B1982" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan mutters quietly while helping Rurichiyo-chan.</t>
+          <t>Rin-chan mutters quietly while helping
+Rurichiyo-chan.</t>
         </is>
       </c>
       <c r="C1982" t="n">
@@ -31017,9 +31040,9 @@
       </c>
       <c r="B1988" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan loosening up is proof she's settling in with
-everyone, and above all I didn't want to spoil the fun
-she's clearly having.</t>
+          <t>Nono-chan loosening up is proof she's settling in
+with everyone, and above all I didn't want to spoil
+the fun she's clearly having.</t>
         </is>
       </c>
       <c r="C1988" t="n">
@@ -31200,8 +31223,8 @@
       </c>
       <c r="B2000" s="1" t="inlineStr">
         <is>
-          <t>The card Nono-chan handed me was a glossy, thick piece
-of cardboard cut evenly to playing-card size.</t>
+          <t>The card Nono-chan handed me was a glossy, thick
+piece of cardboard cut evenly to playing-card size.</t>
         </is>
       </c>
       <c r="C2000" t="n">
@@ -31920,7 +31943,8 @@
       <c r="B2047" s="1" t="inlineStr">
         <is>
           <t>Nono-chan landed on a Special Box again after moving
-six spaces and cheerfully checked the new instruction.</t>
+six spaces and cheerfully checked the new
+instruction.</t>
         </is>
       </c>
       <c r="C2047" t="n">
@@ -31965,7 +31989,8 @@
       </c>
       <c r="B2050" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan dragged her piece back with a downcast face.</t>
+          <t>Nono-chan dragged her piece back with a downcast
+face.</t>
         </is>
       </c>
       <c r="C2050" t="n">
@@ -32410,7 +32435,8 @@
       </c>
       <c r="B2079" s="1" t="inlineStr">
         <is>
-          <t>「Don't worry — I'll have Niini buy it with my coffee.」</t>
+          <t>「Don't worry — I'll have Niini buy it with my
+coffee.」</t>
         </is>
       </c>
       <c r="C2079" t="n">
@@ -32487,8 +32513,8 @@
       </c>
       <c r="B2084" s="1" t="inlineStr">
         <is>
-          <t>「Rin-chan, do you even know what you mean when you say
-that？ If you said it without understanding, then
+          <t>「Rin-chan, do you even know what you mean when you
+say that？ If you said it without understanding, then
 forget talking about expenses.」</t>
         </is>
       </c>
@@ -32976,9 +33002,9 @@
       </c>
       <c r="B2116" s="1" t="inlineStr">
         <is>
-          <t>Because everyone was smiling and urging her, Nono-chan
-let down her guard and tossed a super crispy ume into
-her mouth.</t>
+          <t>Because everyone was smiling and urging her,
+Nono-chan let down her guard and tossed a super
+crispy ume into her mouth.</t>
         </is>
       </c>
       <c r="C2116" t="n">
@@ -33344,8 +33370,8 @@
       </c>
       <c r="B2140" s="1" t="inlineStr">
         <is>
-          <t>Even Rurichiyo-chan, scolding Rin-chan, can’t hide her
-smile.</t>
+          <t>Even Rurichiyo-chan, scolding Rin-chan, can’t hide
+her smile.</t>
         </is>
       </c>
       <c r="C2140" t="n">
@@ -33482,8 +33508,8 @@
       </c>
       <c r="B2149" s="1" t="inlineStr">
         <is>
-          <t>「A-anyway, it’s a mysterious taste！ Feels like a bunch
-of different flavors hit me all at once！」</t>
+          <t>「A-anyway, it’s a mysterious taste！ Feels like a
+bunch of different flavors hit me all at once！」</t>
         </is>
       </c>
       <c r="C2149" t="n">
@@ -34127,7 +34153,8 @@
       </c>
       <c r="B2191" s="1" t="inlineStr">
         <is>
-          <t>「Say naughty words...？ Oh my, I simply won't do that.」</t>
+          <t>「Say naughty words...？ Oh my, I simply won't do
+that.」</t>
         </is>
       </c>
       <c r="C2191" t="n">
@@ -34339,9 +34366,9 @@
       </c>
       <c r="B2205" s="1" t="inlineStr">
         <is>
-          <t>Luck must be on her side today; Nono-chan drew another
-order that lets her eat a snack and she's wearing a
-happy face.</t>
+          <t>Luck must be on her side today; Nono-chan drew
+another order that lets her eat a snack and she's
+wearing a happy face.</t>
         </is>
       </c>
       <c r="C2205" t="n">
@@ -34478,8 +34505,8 @@
       </c>
       <c r="B2214" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan, who's always full of energy no matter what,
-gets happy just from holding the dice.</t>
+          <t>Miru-chan, who's always full of energy no matter
+what, gets happy just from holding the dice.</t>
         </is>
       </c>
       <c r="C2214" t="n">
@@ -34660,8 +34687,8 @@
       </c>
       <c r="B2226" s="1" t="inlineStr">
         <is>
-          <t>Caught up in Nono-chan's cheerful mood, Miru-chan took
-the card with a smile, then suddenly turned it
+          <t>Caught up in Nono-chan's cheerful mood, Miru-chan
+took the card with a smile, then suddenly turned it
 face-down.</t>
         </is>
       </c>
@@ -34737,8 +34764,8 @@
       </c>
       <c r="B2231" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan lets out a strained laugh and asks for it to
-be canceled.</t>
+          <t>Miru-chan lets out a strained laugh and asks for it
+to be canceled.</t>
         </is>
       </c>
       <c r="C2231" t="n">
@@ -35624,7 +35651,8 @@
       <c r="B2289" s="1" t="inlineStr">
         <is>
           <t>...The two involved are practically grinding their
-teeth as they forcefully list the rules to each other.</t>
+teeth as they forcefully list the rules to each
+other.</t>
         </is>
       </c>
       <c r="C2289" t="n">
@@ -35670,8 +35698,8 @@
       </c>
       <c r="B2292" s="1" t="inlineStr">
         <is>
-          <t>「Ufufu... even though we're both girls, aren't we both
-adorable, oji-sama？」</t>
+          <t>「Ufufu... even though we're both girls, aren't we
+both adorable, oji-sama？」</t>
         </is>
       </c>
       <c r="C2292" t="n">
@@ -36085,9 +36113,9 @@
       </c>
       <c r="B2319" s="1" t="inlineStr">
         <is>
-          <t>And even though either of them could back out, they're
-swept up in the mood so that kissing feels like the
-only option.</t>
+          <t>And even though either of them could back out,
+they're swept up in the mood so that kissing feels
+like the only option.</t>
         </is>
       </c>
       <c r="C2319" t="n">
@@ -36923,9 +36951,9 @@
       </c>
       <c r="B2374" s="1" t="inlineStr">
         <is>
-          <t>The two of them, frozen from a light kiss, both pulled
-their faces back at the same time at the cue of
-Rurichiyo-chan's sigh.</t>
+          <t>The two of them, frozen from a light kiss, both
+pulled their faces back at the same time at the cue
+of Rurichiyo-chan's sigh.</t>
         </is>
       </c>
       <c r="C2374" t="n">
@@ -37001,8 +37029,8 @@
       <c r="B2379" s="1" t="inlineStr">
         <is>
           <t>Miru-chan presses her lips and makes a sour face,
-while Rin-chan groans and wipes her lips with the back
-of her hand.</t>
+while Rin-chan groans and wipes her lips with the
+back of her hand.</t>
         </is>
       </c>
       <c r="C2379" t="n">
@@ -37079,8 +37107,8 @@
       <c r="B2384" s="1" t="inlineStr">
         <is>
           <t>Rurichiyo-chan asks me for agreement in a gentle
-voice, but even if she says that I'm at a loss for how
-to answer.</t>
+voice, but even if she says that I'm at a loss for
+how to answer.</t>
         </is>
       </c>
       <c r="C2384" t="n">
@@ -37234,8 +37262,8 @@
       </c>
       <c r="B2394" s="1" t="inlineStr">
         <is>
-          <t>Thinking that and watching them fondly, Rurichiyo-chan
-quietly moved closer to me.</t>
+          <t>Thinking that and watching them fondly,
+Rurichiyo-chan quietly moved closer to me.</t>
         </is>
       </c>
       <c r="C2394" t="n">
@@ -38598,8 +38626,8 @@
       </c>
       <c r="B2483" s="1" t="inlineStr">
         <is>
-          <t>Actually, if you think about it the other way, this is
-a joker card that can become anything.</t>
+          <t>Actually, if you think about it the other way, this
+is a joker card that can become anything.</t>
         </is>
       </c>
       <c r="C2483" t="n">
@@ -38676,8 +38704,8 @@
       </c>
       <c r="B2488" s="1" t="inlineStr">
         <is>
-          <t>But no way I can point at someone by name — that's way
-too obvious.</t>
+          <t>But no way I can point at someone by name — that's
+way too obvious.</t>
         </is>
       </c>
       <c r="C2488" t="n">
@@ -39163,8 +39191,8 @@
       </c>
       <c r="B2520" s="1" t="inlineStr">
         <is>
-          <t>This time, saying it firmly, Nono-chan went bright red
-and began to panic.</t>
+          <t>This time, saying it firmly, Nono-chan went bright
+red and began to panic.</t>
         </is>
       </c>
       <c r="C2520" t="n">
@@ -39394,8 +39422,8 @@
       </c>
       <c r="B2535" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan looks wistful, like a mother seeing her
-beloved daughter off to be married.</t>
+          <t>Rurichiyo-chan looks wistful, like a mother seeing
+her beloved daughter off to be married.</t>
         </is>
       </c>
       <c r="C2535" t="n">
@@ -39471,8 +39499,8 @@
       </c>
       <c r="B2540" s="1" t="inlineStr">
         <is>
-          <t>I got carried away and said it by myself — I shouldn't
-have not thought about the aftereffects.</t>
+          <t>I got carried away and said it by myself — I
+shouldn't have not thought about the aftereffects.</t>
         </is>
       </c>
       <c r="C2540" t="n">
@@ -39594,8 +39622,8 @@
       </c>
       <c r="B2548" s="1" t="inlineStr">
         <is>
-          <t>…I got scared for a moment, but Nono-chan doesn't seem
-to be refusing.</t>
+          <t>…I got scared for a moment, but Nono-chan doesn't
+seem to be refusing.</t>
         </is>
       </c>
       <c r="C2548" t="n">
@@ -39911,8 +39939,8 @@
       </c>
       <c r="B2569" s="1" t="inlineStr">
         <is>
-          <t>I scooted forward on my knees and sat down in front of
-Nono-chan.</t>
+          <t>I scooted forward on my knees and sat down in front
+of Nono-chan.</t>
         </is>
       </c>
       <c r="C2569" t="n">
@@ -40094,8 +40122,8 @@
       </c>
       <c r="B2581" s="1" t="inlineStr">
         <is>
-          <t>They stuck out their tongue and licked their lips, and
-their lips gave a sudden little twitch.</t>
+          <t>They stuck out their tongue and licked their lips,
+and their lips gave a sudden little twitch.</t>
         </is>
       </c>
       <c r="C2581" t="n">
@@ -40246,8 +40274,8 @@
       </c>
       <c r="B2591" s="1" t="inlineStr">
         <is>
-          <t>Because they're so earnest, they must be noticing what
-I'm doing and copying me.</t>
+          <t>Because they're so earnest, they must be noticing
+what I'm doing and copying me.</t>
         </is>
       </c>
       <c r="C2591" t="n">
@@ -40415,9 +40443,9 @@
       </c>
       <c r="B2602" s="1" t="inlineStr">
         <is>
-          <t>But Nono-chan, who doesn’t know her limits, won’t stop
-using her tongue even when she starts to have trouble
-breathing.</t>
+          <t>But Nono-chan, who doesn’t know her limits, won’t
+stop using her tongue even when she starts to have
+trouble breathing.</t>
         </is>
       </c>
       <c r="C2602" t="n">
@@ -40615,8 +40643,8 @@
       </c>
       <c r="B2615" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan, her face bright red, hung her head and just
-stood there frozen.</t>
+          <t>Nono-chan, her face bright red, hung her head and
+just stood there frozen.</t>
         </is>
       </c>
       <c r="C2615" t="n">
@@ -42159,7 +42187,8 @@
       <c r="B2716" s="1" t="inlineStr">
         <is>
           <t>Hmm... they're frustrated they can't talk back, but
-the fact they don't refuse... means they're into you！？</t>
+the fact they don't refuse... means they're into
+you！？</t>
         </is>
       </c>
       <c r="C2716" t="n">
@@ -42387,8 +42416,8 @@
       </c>
       <c r="B2731" s="1" t="inlineStr">
         <is>
-          <t>When I glance over, Nono-chan is frozen, letting out a
-small groan.</t>
+          <t>When I glance over, Nono-chan is frozen, letting out
+a small groan.</t>
         </is>
       </c>
       <c r="C2731" t="n">
@@ -42740,8 +42769,8 @@
       </c>
       <c r="B2754" s="1" t="inlineStr">
         <is>
-          <t>Even so, Miru-chan staying still and enduring it is so
-cute.</t>
+          <t>Even so, Miru-chan staying still and enduring it is
+so cute.</t>
         </is>
       </c>
       <c r="C2754" t="n">
@@ -42983,8 +43012,8 @@
       </c>
       <c r="B2770" s="1" t="inlineStr">
         <is>
-          <t>Surprised by the kiss, Miru-chan obediently opened her
-mouth at my words.</t>
+          <t>Surprised by the kiss, Miru-chan obediently opened
+her mouth at my words.</t>
         </is>
       </c>
       <c r="C2770" t="n">
@@ -43779,8 +43808,8 @@
       </c>
       <c r="B2822" s="1" t="inlineStr">
         <is>
-          <t>When I timidly looked for Nono-chan, I saw her picking
-up the card I'd left face-down.</t>
+          <t>When I timidly looked for Nono-chan, I saw her
+picking up the card I'd left face-down.</t>
         </is>
       </c>
       <c r="C2822" t="n">
@@ -44067,8 +44096,9 @@
       </c>
       <c r="B2841" s="1" t="inlineStr">
         <is>
-          <t>Third-place Rin-chan kept shouting no way, shaking her
-head and even waving her hands in a rejecting gesture.</t>
+          <t>Third-place Rin-chan kept shouting no way, shaking
+her head and even waving her hands in a rejecting
+gesture.</t>
         </is>
       </c>
       <c r="C2841" t="n">
@@ -44113,8 +44143,8 @@
       </c>
       <c r="B2844" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan, making a rare wicked face, started chanting
-with a sing-song tease.</t>
+          <t>Miru-chan, making a rare wicked face, started
+chanting with a sing-song tease.</t>
         </is>
       </c>
       <c r="C2844" t="n">
@@ -44174,8 +44204,8 @@
       </c>
       <c r="B2848" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan, also amused, copied Miru-chan to tease
-her.</t>
+          <t>Rurichiyo-chan, also amused, copied Miru-chan to
+tease her.</t>
         </is>
       </c>
       <c r="C2848" t="n">
@@ -44267,8 +44297,8 @@
       </c>
       <c r="B2854" s="1" t="inlineStr">
         <is>
-          <t>If this keeps up, Rin-chan will go along with the mood
-and it'll just be written off as a joke.</t>
+          <t>If this keeps up, Rin-chan will go along with the
+mood and it'll just be written off as a joke.</t>
         </is>
       </c>
       <c r="C2854" t="n">
@@ -44283,8 +44313,8 @@
       </c>
       <c r="B2855" s="1" t="inlineStr">
         <is>
-          <t>But if she takes it seriously, they'll all gang up and
-scold me…</t>
+          <t>But if she takes it seriously, they'll all gang up
+and scold me…</t>
         </is>
       </c>
       <c r="C2855" t="n">
@@ -45095,8 +45125,8 @@
       </c>
       <c r="B2908" s="1" t="inlineStr">
         <is>
-          <t>Before I knew it, Rin-chan's lips were pressed against
-mine.</t>
+          <t>Before I knew it, Rin-chan's lips were pressed
+against mine.</t>
         </is>
       </c>
       <c r="C2908" t="n">
@@ -45157,8 +45187,8 @@
       </c>
       <c r="B2912" s="1" t="inlineStr">
         <is>
-          <t>But just as my mind caught up with what was happening,
-I felt my lips start to part.</t>
+          <t>But just as my mind caught up with what was
+happening, I felt my lips start to part.</t>
         </is>
       </c>
       <c r="C2912" t="n">
@@ -45755,7 +45785,8 @@
       <c r="B2951" s="1" t="inlineStr">
         <is>
           <t>I felt disappointed for a moment, but when I looked
-again Rin-chan's face was melting, flushed bright red.</t>
+again Rin-chan's face was melting, flushed bright
+red.</t>
         </is>
       </c>
       <c r="C2951" t="n">
@@ -45847,8 +45878,8 @@
       </c>
       <c r="B2957" s="1" t="inlineStr">
         <is>
-          <t>It's probably just to hide her embarrassment... ahaha,
-so cute...</t>
+          <t>It's probably just to hide her embarrassment...
+ahaha, so cute...</t>
         </is>
       </c>
       <c r="C2957" t="n">
@@ -46015,8 +46046,8 @@
       </c>
       <c r="B2968" s="1" t="inlineStr">
         <is>
-          <t>Even though they were hiding it with a sheet, the fact
-we were kissing must have come through.</t>
+          <t>Even though they were hiding it with a sheet, the
+fact we were kissing must have come through.</t>
         </is>
       </c>
       <c r="C2968" t="n">
@@ -46275,9 +46306,9 @@
       </c>
       <c r="B2985" s="1" t="inlineStr">
         <is>
-          <t>I was asked to make some kind of excuse, but since I'm
-secretly happier about it, I don't even have the mind
-to come up with one.</t>
+          <t>I was asked to make some kind of excuse, but since
+I'm secretly happier about it, I don't even have the
+mind to come up with one.</t>
         </is>
       </c>
       <c r="C2985" t="n">
@@ -46672,8 +46703,8 @@
       </c>
       <c r="B3011" s="1" t="inlineStr">
         <is>
-          <t>Even though it was a blank card, I went and made up my
-own order.</t>
+          <t>Even though it was a blank card, I went and made up
+my own order.</t>
         </is>
       </c>
       <c r="C3011" t="n">
@@ -47010,8 +47041,9 @@
       </c>
       <c r="B3033" s="1" t="inlineStr">
         <is>
-          <t>If it were between girls, that might be different, but
-an order to kiss a guy is probably just too intense.</t>
+          <t>If it were between girls, that might be different,
+but an order to kiss a guy is probably just too
+intense.</t>
         </is>
       </c>
       <c r="C3033" t="n">
@@ -47056,8 +47088,8 @@
       </c>
       <c r="B3036" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan herself was flustered, and she'd gotten
-tongue-tied.</t>
+          <t>Rurichiyo-chan herself was flustered, and she'd
+gotten tongue-tied.</t>
         </is>
       </c>
       <c r="C3036" t="n">
@@ -47118,7 +47150,8 @@
       </c>
       <c r="B3040" s="1" t="inlineStr">
         <is>
-          <t>Or rather, it already feels like they're freaking out.</t>
+          <t>Or rather, it already feels like they're freaking
+out.</t>
         </is>
       </c>
       <c r="C3040" t="n">
@@ -47178,7 +47211,8 @@
       </c>
       <c r="B3044" s="1" t="inlineStr">
         <is>
-          <t>「That's right！ Don't you dare try to take me lightly！」</t>
+          <t>「That's right！ Don't you dare try to take me
+lightly！」</t>
         </is>
       </c>
       <c r="C3044" t="n">
@@ -47409,8 +47443,8 @@
       </c>
       <c r="B3059" s="1" t="inlineStr">
         <is>
-          <t>「After all, oji-sama and I have known each other for a
-long time… it’s like family affection, you know.」</t>
+          <t>「After all, oji-sama and I have known each other for
+a long time… it’s like family affection, you know.」</t>
         </is>
       </c>
       <c r="C3059" t="n">
@@ -47426,8 +47460,8 @@
       <c r="B3060" s="1" t="inlineStr">
         <is>
           <t>Rurichiyo-chan is Rurichiyo-chan, and she’s going
-ahead all by herself with a story that already assumes
-a kiss.</t>
+ahead all by herself with a story that already
+assumes a kiss.</t>
         </is>
       </c>
       <c r="C3060" t="n">
@@ -47595,8 +47629,8 @@
       </c>
       <c r="B3071" s="1" t="inlineStr">
         <is>
-          <t>While I'm lost in thoughts, Rurichiyo-chan has totally
-gotten into it.</t>
+          <t>While I'm lost in thoughts, Rurichiyo-chan has
+totally gotten into it.</t>
         </is>
       </c>
       <c r="C3071" t="n">
@@ -47748,8 +47782,8 @@
       </c>
       <c r="B3081" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan's face, eyes squeezed shut, trembles as
-if she's holding something back.</t>
+          <t>Rurichiyo-chan's face, eyes squeezed shut, trembles
+as if she's holding something back.</t>
         </is>
       </c>
       <c r="C3081" t="n">
@@ -47764,8 +47798,8 @@
       </c>
       <c r="B3082" s="1" t="inlineStr">
         <is>
-          <t>I kinda created the situation on a whim, but I'm still
-nervous inwardly.</t>
+          <t>I kinda created the situation on a whim, but I'm
+still nervous inwardly.</t>
         </is>
       </c>
       <c r="C3082" t="n">
@@ -48070,7 +48104,8 @@
       </c>
       <c r="B3102" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan nibbled her lips in the same way I did.</t>
+          <t>Rurichiyo-chan nibbled her lips in the same way I
+did.</t>
         </is>
       </c>
       <c r="C3102" t="n">
@@ -48449,8 +48484,8 @@
       </c>
       <c r="B3127" s="1" t="inlineStr">
         <is>
-          <t>When I opened my eyes a little, I met Rurichiyo-chan’s
-half-opened gaze as well.</t>
+          <t>When I opened my eyes a little, I met
+Rurichiyo-chan’s half-opened gaze as well.</t>
         </is>
       </c>
       <c r="C3127" t="n">
@@ -48465,8 +48500,8 @@
       </c>
       <c r="B3128" s="1" t="inlineStr">
         <is>
-          <t>And somehow… the kindness in her eyes struck me to the
-heart.</t>
+          <t>And somehow… the kindness in her eyes struck me to
+the heart.</t>
         </is>
       </c>
       <c r="C3128" t="n">
@@ -48511,8 +48546,8 @@
       </c>
       <c r="B3131" s="1" t="inlineStr">
         <is>
-          <t>…Even though we were making embarrassingly wet kissing
-noises, I lost myself in the kiss.</t>
+          <t>…Even though we were making embarrassingly wet
+kissing noises, I lost myself in the kiss.</t>
         </is>
       </c>
       <c r="C3131" t="n">
@@ -48899,7 +48934,8 @@
       </c>
       <c r="B3156" s="1" t="inlineStr">
         <is>
-          <t>...If she hadn't stopped us, it would've kept going...</t>
+          <t>...If she hadn't stopped us, it would've kept
+going...</t>
         </is>
       </c>
       <c r="C3156" t="n">
@@ -49356,9 +49392,9 @@
       </c>
       <c r="B3186" s="1" t="inlineStr">
         <is>
-          <t>...While everyone was recovering from the shock of the
-kiss and calming down, I kept bowing and apologizing
-nonstop.</t>
+          <t>...While everyone was recovering from the shock of
+the kiss and calming down, I kept bowing and
+apologizing nonstop.</t>
         </is>
       </c>
       <c r="C3186" t="n">
@@ -49419,8 +49455,8 @@
       </c>
       <c r="B3190" s="1" t="inlineStr">
         <is>
-          <t>「So, about Janitor-sensei who cheated, what do you all
-think we should do？」</t>
+          <t>「So, about Janitor-sensei who cheated, what do you
+all think we should do？」</t>
         </is>
       </c>
       <c r="C3190" t="n">
@@ -49891,9 +49927,9 @@
       </c>
       <c r="B3221" s="1" t="inlineStr">
         <is>
-          <t>In Makishima, surrounded by the sea, you can eat fresh
-fish cheaply, but when it comes to the 'special' set,
-it really costs a lot.</t>
+          <t>In Makishima, surrounded by the sea, you can eat
+fresh fish cheaply, but when it comes to the
+'special' set, it really costs a lot.</t>
         </is>
       </c>
       <c r="C3221" t="n">
@@ -49909,8 +49945,8 @@
       <c r="B3222" s="1" t="inlineStr">
         <is>
           <t>Especially sushi chefs, because they can buy fish
-cheaply, have a keen eye for fish and are confident in
-their ability to judge quality.</t>
+cheaply, have a keen eye for fish and are confident
+in their ability to judge quality.</t>
         </is>
       </c>
       <c r="C3222" t="n">
@@ -50063,8 +50099,8 @@
       <c r="B3232" s="1" t="inlineStr">
         <is>
           <t>Rather than thinking of it as a penalty, if you think
-of it as treating her to premium sushi because of that
-sight, it's a small price to pay.</t>
+of it as treating her to premium sushi because of
+that sight, it's a small price to pay.</t>
         </is>
       </c>
       <c r="C3232" t="n">
@@ -50201,8 +50237,8 @@
       </c>
       <c r="B3241" s="1" t="inlineStr">
         <is>
-          <t>I couldn't help but butt in, but Rurichiyo-chan smiled
-and nodded.</t>
+          <t>I couldn't help but butt in, but Rurichiyo-chan
+smiled and nodded.</t>
         </is>
       </c>
       <c r="C3241" t="n">
@@ -51057,8 +51093,9 @@
       </c>
       <c r="B3297" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan imitated what Rurichiyo-chan did, flipped up
-the topping and scraped off the wasabi with a spoon.</t>
+          <t>Nono-chan imitated what Rurichiyo-chan did, flipped
+up the topping and scraped off the wasabi with a
+spoon.</t>
         </is>
       </c>
       <c r="C3297" t="n">
@@ -51347,8 +51384,8 @@
       </c>
       <c r="B3316" s="1" t="inlineStr">
         <is>
-          <t>Next, what Rin-chan pointed out was the ikura — fresh,
-translucent, and visually vibrant.</t>
+          <t>Next, what Rin-chan pointed out was the ikura —
+fresh, translucent, and visually vibrant.</t>
         </is>
       </c>
       <c r="C3316" t="n">
@@ -52025,7 +52062,8 @@
       <c r="B3360" s="1" t="inlineStr">
         <is>
           <t>「Y-yes！ At first it was spicy, spicy, spicy... but,
-um, I thought the soy sauce flavor was very Japanese！」</t>
+um, I thought the soy sauce flavor was very
+Japanese！」</t>
         </is>
       </c>
       <c r="C3360" t="n">
@@ -52221,8 +52259,8 @@
       </c>
       <c r="B3373" s="1" t="inlineStr">
         <is>
-          <t>When Miru-chan spoke up, everyone started naming their
-favorite toppings.</t>
+          <t>When Miru-chan spoke up, everyone started naming
+their favorite toppings.</t>
         </is>
       </c>
       <c r="C3373" t="n">
@@ -52531,7 +52569,8 @@
       <c r="B3393" s="1" t="inlineStr">
         <is>
           <t>When Rurichiyo-chan chimed in, Nono-chan spread out
-the sugoroku she’d brought from the bus and showed it.</t>
+the sugoroku she’d brought from the bus and showed
+it.</t>
         </is>
       </c>
       <c r="C3393" t="n">
@@ -52713,8 +52752,8 @@
       </c>
       <c r="B3405" s="1" t="inlineStr">
         <is>
-          <t>Pleasure at everyone's reactions or not, Nono-chan put
-on a prim face and crossed her arms.</t>
+          <t>Pleasure at everyone's reactions or not, Nono-chan
+put on a prim face and crossed her arms.</t>
         </is>
       </c>
       <c r="C3405" t="n">
@@ -52884,8 +52923,8 @@
       </c>
       <c r="B3416" s="1" t="inlineStr">
         <is>
-          <t>I don't know what she noticed, but it's something only
-Nono-chan knows, so let's stay quiet and watch.</t>
+          <t>I don't know what she noticed, but it's something
+only Nono-chan knows, so let's stay quiet and watch.</t>
         </is>
       </c>
       <c r="C3416" t="n">
@@ -53867,8 +53906,8 @@
       </c>
       <c r="B3480" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan tilts her head, and then starts to twist her
-neck as well.</t>
+          <t>Nono-chan tilts her head, and then starts to twist
+her neck as well.</t>
         </is>
       </c>
       <c r="C3480" t="n">
@@ -53883,8 +53922,8 @@
       </c>
       <c r="B3481" s="1" t="inlineStr">
         <is>
-          <t>Even with this prodigy's brain, it looks like cracking
-this cipher would be tough.</t>
+          <t>Even with this prodigy's brain, it looks like
+cracking this cipher would be tough.</t>
         </is>
       </c>
       <c r="C3481" t="n">
@@ -54251,7 +54290,8 @@
       </c>
       <c r="B3505" s="1" t="inlineStr">
         <is>
-          <t>「I'll write it down... In Makishima, 'Me' ga mieru...」</t>
+          <t>「I'll write it down... In Makishima, 'Me' ga
+mieru...」</t>
         </is>
       </c>
       <c r="C3505" t="n">
@@ -54327,8 +54367,8 @@
       </c>
       <c r="B3510" s="1" t="inlineStr">
         <is>
-          <t>「I understand now too！ The 'Me' is actually an X mark,
-isn't it?」</t>
+          <t>「I understand now too！ The 'Me' is actually an X
+mark, isn't it?」</t>
         </is>
       </c>
       <c r="C3510" t="n">
@@ -54480,8 +54520,8 @@
       </c>
       <c r="B3520" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan nods meaningfully, but she doesn't look like
-she understands how Miru-chan solved it.</t>
+          <t>Nono-chan nods meaningfully, but she doesn't look
+like she understands how Miru-chan solved it.</t>
         </is>
       </c>
       <c r="C3520" t="n">
@@ -54725,9 +54765,9 @@
       </c>
       <c r="B3536" s="1" t="inlineStr">
         <is>
-          <t>In the end we only learned that even Nono-chan doesn't
-understand, but she's impressive for having a way to
-flip her thinking.</t>
+          <t>In the end we only learned that even Nono-chan
+doesn't understand, but she's impressive for having a
+way to flip her thinking.</t>
         </is>
       </c>
       <c r="C3536" t="n">
@@ -54866,8 +54906,8 @@
       </c>
       <c r="B3545" s="1" t="inlineStr">
         <is>
-          <t>「...That's why only the 'ki' character has a different
-color.」</t>
+          <t>「...That's why only the 'ki' character has a
+different color.」</t>
         </is>
       </c>
       <c r="C3545" t="n">
@@ -54929,8 +54969,8 @@
       </c>
       <c r="B3549" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan, who quickly picked up on what Rin-chan
-meant, took over speaking.</t>
+          <t>Rurichiyo-chan, who quickly picked up on what
+Rin-chan meant, took over speaking.</t>
         </is>
       </c>
       <c r="C3549" t="n">
@@ -55129,8 +55169,8 @@
       </c>
       <c r="B3562" s="1" t="inlineStr">
         <is>
-          <t>「Uh, um… well then… let's first think about what the X
-mark is supposed to mean！」</t>
+          <t>「Uh, um… well then… let's first think about what the
+X mark is supposed to mean！」</t>
         </is>
       </c>
       <c r="C3562" t="n">
@@ -55160,8 +55200,8 @@
       </c>
       <c r="B3564" s="1" t="inlineStr">
         <is>
-          <t>「If we assume what the X mark represents and reason to
-match that, we should be able to figure it out！」</t>
+          <t>「If we assume what the X mark represents and reason
+to match that, we should be able to figure it out！」</t>
         </is>
       </c>
       <c r="C3564" t="n">
@@ -55697,8 +55737,8 @@
       <c r="B3599" s="1" t="inlineStr">
         <is>
           <t>I feel like I'd be able to go by bus and be done
-quickly, but judging from the map the X mark is in the
-mountains.</t>
+quickly, but judging from the map the X mark is in
+the mountains.</t>
         </is>
       </c>
       <c r="C3599" t="n">
@@ -55713,9 +55753,9 @@
       </c>
       <c r="B3600" s="1" t="inlineStr">
         <is>
-          <t>It's fine to go as a noisy group, but if it takes time
-and we get caught on mountain roads after dark, that
-would be troublesome.</t>
+          <t>It's fine to go as a noisy group, but if it takes
+time and we get caught on mountain roads after dark,
+that would be troublesome.</t>
         </is>
       </c>
       <c r="C3600" t="n">
@@ -56217,8 +56257,8 @@
       </c>
       <c r="B3633" s="1" t="inlineStr">
         <is>
-          <t>Makishima alone would be livable, but the selection is
-pretty limited — maybe I should pick up a bunch of
+          <t>Makishima alone would be livable, but the selection
+is pretty limited — maybe I should pick up a bunch of
 things at once…？</t>
         </is>
       </c>
@@ -56726,8 +56766,8 @@
       </c>
       <c r="B3666" s="1" t="inlineStr">
         <is>
-          <t>However, unlucky for us the bus loading wait was long,
-so everyone was already bored.</t>
+          <t>However, unlucky for us the bus loading wait was
+long, so everyone was already bored.</t>
         </is>
       </c>
       <c r="C3666" t="n">
@@ -57141,8 +57181,8 @@
       </c>
       <c r="B3693" s="1" t="inlineStr">
         <is>
-          <t>She's usually not the type to show desire, so Rin-chan
-looks back at her with keen interest.</t>
+          <t>She's usually not the type to show desire, so
+Rin-chan looks back at her with keen interest.</t>
         </is>
       </c>
       <c r="C3693" t="n">
@@ -57696,9 +57736,9 @@
       </c>
       <c r="B3729" s="1" t="inlineStr">
         <is>
-          <t>「Ah, Rurichiyo-chan, don't you have something you want
-to see？ Since we're here, why don't you go take a
-look？」</t>
+          <t>「Ah, Rurichiyo-chan, don't you have something you
+want to see？ Since we're here, why don't you go take
+a look？」</t>
         </is>
       </c>
       <c r="C3729" t="n">
@@ -57881,8 +57921,8 @@
       </c>
       <c r="B3741" s="1" t="inlineStr">
         <is>
-          <t>「Hmm... let's see. Nothing in particular comes to mind
-right now...」</t>
+          <t>「Hmm... let's see. Nothing in particular comes to
+mind right now...」</t>
         </is>
       </c>
       <c r="C3741" t="n">
@@ -58003,7 +58043,8 @@
       </c>
       <c r="B3749" s="1" t="inlineStr">
         <is>
-          <t>My attention gradually turned to inspecting the items.</t>
+          <t>My attention gradually turned to inspecting the
+items.</t>
         </is>
       </c>
       <c r="C3749" t="n">
@@ -58327,8 +58368,8 @@
       </c>
       <c r="B3770" s="1" t="inlineStr">
         <is>
-          <t>...But after a little while, Nono-chan started looking
-around restlessly.</t>
+          <t>...But after a little while, Nono-chan started
+looking around restlessly.</t>
         </is>
       </c>
       <c r="C3770" t="n">
@@ -58403,8 +58444,8 @@
       </c>
       <c r="B3775" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan fluttered her hands and made a face like she
-was trying to cover something up.</t>
+          <t>Nono-chan fluttered her hands and made a face like
+she was trying to cover something up.</t>
         </is>
       </c>
       <c r="C3775" t="n">
@@ -58494,8 +58535,8 @@
       </c>
       <c r="B3781" s="1" t="inlineStr">
         <is>
-          <t>When I pointed at the cart's step, Nono-chan fluttered
-her hands again.</t>
+          <t>When I pointed at the cart's step, Nono-chan
+fluttered her hands again.</t>
         </is>
       </c>
       <c r="C3781" t="n">
@@ -59014,8 +59055,8 @@
       </c>
       <c r="B3815" s="1" t="inlineStr">
         <is>
-          <t>Hmm, true — when you say you coordinate princesses, it
-might sound like an elegant game.</t>
+          <t>Hmm, true — when you say you coordinate princesses,
+it might sound like an elegant game.</t>
         </is>
       </c>
       <c r="C3815" t="n">
@@ -59229,7 +59270,8 @@
       <c r="B3829" s="1" t="inlineStr">
         <is>
           <t>Looking for a word that's casual to use and can be
-broadly interpreted, I thought of saying 'recreation'.</t>
+broadly interpreted, I thought of saying
+'recreation'.</t>
         </is>
       </c>
       <c r="C3829" t="n">
@@ -59548,8 +59590,8 @@
       </c>
       <c r="B3850" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan picked out a few of the snacks she’d just put
-in the basket and went to put them back on the
+          <t>Rin-chan picked out a few of the snacks she’d just
+put in the basket and went to put them back on the
 original shelf.</t>
         </is>
       </c>
@@ -60055,8 +60097,8 @@
       </c>
       <c r="B3883" s="1" t="inlineStr">
         <is>
-          <t>「If you're going to ride a cart, how about taking this
-one？」</t>
+          <t>「If you're going to ride a cart, how about taking
+this one？」</t>
         </is>
       </c>
       <c r="C3883" t="n">
@@ -60271,8 +60313,8 @@
       </c>
       <c r="B3897" s="1" t="inlineStr">
         <is>
-          <t>She should've been eager to get in, but she gulped and
-hastily backed away from the cart.</t>
+          <t>She should've been eager to get in, but she gulped
+and hastily backed away from the cart.</t>
         </is>
       </c>
       <c r="C3897" t="n">
@@ -60362,8 +60404,9 @@
       </c>
       <c r="B3903" s="1" t="inlineStr">
         <is>
-          <t>When I looked over, Rurichiyo-chan showed me something
-she was holding protectively with both hands.</t>
+          <t>When I looked over, Rurichiyo-chan showed me
+something she was holding protectively with both
+hands.</t>
         </is>
       </c>
       <c r="C3903" t="n">
@@ -60594,8 +60637,8 @@
       </c>
       <c r="B3918" s="1" t="inlineStr">
         <is>
-          <t>「Ah... you don't have to return it. If you want to eat
-it I'll buy it for you.」</t>
+          <t>「Ah... you don't have to return it. If you want to
+eat it I'll buy it for you.」</t>
         </is>
       </c>
       <c r="C3918" t="n">
@@ -60687,8 +60730,8 @@
       </c>
       <c r="B3924" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan, who usually smiles gently, was showing
-an innocent grin.</t>
+          <t>Rurichiyo-chan, who usually smiles gently, was
+showing an innocent grin.</t>
         </is>
       </c>
       <c r="C3924" t="n">
@@ -60718,8 +60761,8 @@
       </c>
       <c r="B3926" s="1" t="inlineStr">
         <is>
-          <t>...Or rather, I didn't expect someone to be this happy
-over cup ramen...</t>
+          <t>...Or rather, I didn't expect someone to be this
+happy over cup ramen...</t>
         </is>
       </c>
       <c r="C3926" t="n">
@@ -60796,8 +60839,8 @@
       <c r="B3931" s="1" t="inlineStr">
         <is>
           <t>Rurichiyo-chan, all excited, said that and then ran
-off while still holding the cup of instant ramen she'd
-just brought.</t>
+off while still holding the cup of instant ramen
+she'd just brought.</t>
         </is>
       </c>
       <c r="C3931" t="n">
@@ -61287,8 +61330,8 @@
       </c>
       <c r="B3963" s="1" t="inlineStr">
         <is>
-          <t>「Th-there are whole fish being sold like this！ Can you
-cook something like that at home？」</t>
+          <t>「Th-there are whole fish being sold like this！ Can
+you cook something like that at home？」</t>
         </is>
       </c>
       <c r="C3963" t="n">
@@ -61492,8 +61535,8 @@
       </c>
       <c r="B3976" s="1" t="inlineStr">
         <is>
-          <t>「Ahaha... I haven't learned Japanese cooking yet, so I
-can't really say...」</t>
+          <t>「Ahaha... I haven't learned Japanese cooking yet, so
+I can't really say...」</t>
         </is>
       </c>
       <c r="C3976" t="n">
@@ -61540,8 +61583,8 @@
       </c>
       <c r="B3979" s="1" t="inlineStr">
         <is>
-          <t>「Then next time, how about you make your English food,
-Nono-chan？」</t>
+          <t>「Then next time, how about you make your English
+food, Nono-chan？」</t>
         </is>
       </c>
       <c r="C3979" t="n">
@@ -62080,7 +62123,8 @@
       </c>
       <c r="B4014" s="1" t="inlineStr">
         <is>
-          <t>「Nice, Nono-chan. Miru wants to ride in the cart too.」</t>
+          <t>「Nice, Nono-chan. Miru wants to ride in the cart
+too.」</t>
         </is>
       </c>
       <c r="C4014" t="n">
@@ -62295,8 +62339,8 @@
       </c>
       <c r="B4028" s="1" t="inlineStr">
         <is>
-          <t>Since we loaded the bus onto the ferry, we didn't have
-to carry heavy luggage, but I was still a little
+          <t>Since we loaded the bus onto the ferry, we didn't
+have to carry heavy luggage, but I was still a little
 tired.</t>
         </is>
       </c>
@@ -62421,9 +62465,9 @@
       </c>
       <c r="B4036" s="1" t="inlineStr">
         <is>
-          <t>Except when I'm working or sleeping, I'm always taking
-care of someone, so being with everyone has become
-normal for me.</t>
+          <t>Except when I'm working or sleeping, I'm always
+taking care of someone, so being with everyone has
+become normal for me.</t>
         </is>
       </c>
       <c r="C4036" t="n">
@@ -62852,8 +62896,8 @@
       </c>
       <c r="B4064" s="1" t="inlineStr">
         <is>
-          <t>……I feel relieved, but this isn't a situation to relax
-in！</t>
+          <t>……I feel relieved, but this isn't a situation to
+relax in！</t>
         </is>
       </c>
       <c r="C4064" t="n">
@@ -62974,8 +63018,8 @@
       </c>
       <c r="B4072" s="1" t="inlineStr">
         <is>
-          <t>「...Adults sometimes take forever in the bathroom, you
-know.」</t>
+          <t>「...Adults sometimes take forever in the bathroom,
+you know.」</t>
         </is>
       </c>
       <c r="C4072" t="n">
@@ -63005,9 +63049,9 @@
       </c>
       <c r="B4074" s="1" t="inlineStr">
         <is>
-          <t>Most likely there's some old guy treating it like mine
-own house, spreading out a newspaper in the toilet, I
-figure.</t>
+          <t>Most likely there's some old guy treating it like
+mine own house, spreading out a newspaper in the
+toilet, I figure.</t>
         </is>
       </c>
       <c r="C4074" t="n">
@@ -63463,8 +63507,8 @@
       </c>
       <c r="B4104" s="1" t="inlineStr">
         <is>
-          <t>I gently called out as I quietly moved behind Rin-chan
-and crouched down….</t>
+          <t>I gently called out as I quietly moved behind
+Rin-chan and crouched down….</t>
         </is>
       </c>
       <c r="C4104" t="n">
@@ -63709,8 +63753,8 @@
       </c>
       <c r="B4120" s="1" t="inlineStr">
         <is>
-          <t>After I said that, I reconsidered and thought I should
-have spoken more gently.</t>
+          <t>After I said that, I reconsidered and thought I
+should have spoken more gently.</t>
         </is>
       </c>
       <c r="C4120" t="n">
@@ -63817,7 +63861,8 @@
       </c>
       <c r="B4127" s="1" t="inlineStr">
         <is>
-          <t>Hmm... it looks like her embarrassment is winning out.</t>
+          <t>Hmm... it looks like her embarrassment is winning
+out.</t>
         </is>
       </c>
       <c r="C4127" t="n">
@@ -64075,8 +64120,8 @@
       </c>
       <c r="B4144" s="1" t="inlineStr">
         <is>
-          <t>Every time Rin-chan spoke a single word she groaned in
-pain.</t>
+          <t>Every time Rin-chan spoke a single word she groaned
+in pain.</t>
         </is>
       </c>
       <c r="C4144" t="n">
@@ -64247,7 +64292,8 @@
       </c>
       <c r="B4155" s="1" t="inlineStr">
         <is>
-          <t>「Guess it can't be helped... I'll put you down, then.」</t>
+          <t>「Guess it can't be helped... I'll put you down,
+then.」</t>
         </is>
       </c>
       <c r="C4155" t="n">
@@ -64324,8 +64370,8 @@
       </c>
       <c r="B4160" s="1" t="inlineStr">
         <is>
-          <t>But bringing it up again would just complicate things,
-so let's move the conversation forward as is.</t>
+          <t>But bringing it up again would just complicate
+things, so let's move the conversation forward as is.</t>
         </is>
       </c>
       <c r="C4160" t="n">
@@ -64537,8 +64583,8 @@
       <c r="B4174" s="1" t="inlineStr">
         <is>
           <t>If I put it in a deliberately light-hearted way, even
-the usually formidable Rin-chan seems to have lost her
-edge.</t>
+the usually formidable Rin-chan seems to have lost
+her edge.</t>
         </is>
       </c>
       <c r="C4174" t="n">
@@ -64844,8 +64890,8 @@
       </c>
       <c r="B4194" s="1" t="inlineStr">
         <is>
-          <t>I'd absentmindedly been thinking weird thoughts, so my
-grip loosened without me noticing.</t>
+          <t>I'd absentmindedly been thinking weird thoughts, so
+my grip loosened without me noticing.</t>
         </is>
       </c>
       <c r="C4194" t="n">
@@ -65194,7 +65240,8 @@
       </c>
       <c r="B4217" s="1" t="inlineStr">
         <is>
-          <t>Did you get so nervous that you ended up pulling back？</t>
+          <t>Did you get so nervous that you ended up pulling
+back？</t>
         </is>
       </c>
       <c r="C4217" t="n">
@@ -65526,8 +65573,8 @@
       </c>
       <c r="B4239" s="1" t="inlineStr">
         <is>
-          <t>While scolding me, Rin-chan tightened her grip between
-her legs.</t>
+          <t>While scolding me, Rin-chan tightened her grip
+between her legs.</t>
         </is>
       </c>
       <c r="C4239" t="n">
@@ -66047,8 +66094,8 @@
       </c>
       <c r="B4273" s="1" t="inlineStr">
         <is>
-          <t>Watching them like that, I feel like I’m going to feel
-good...</t>
+          <t>Watching them like that, I feel like I’m going to
+feel good...</t>
         </is>
       </c>
       <c r="C4273" t="n">
@@ -66427,7 +66474,8 @@
       </c>
       <c r="B4298" s="1" t="inlineStr">
         <is>
-          <t>Following Miru-chan, Nono-chan came out onto the deck.</t>
+          <t>Following Miru-chan, Nono-chan came out onto the
+deck.</t>
         </is>
       </c>
       <c r="C4298" t="n">
@@ -66730,8 +66778,8 @@
       </c>
       <c r="B4318" s="1" t="inlineStr">
         <is>
-          <t>As I was thinking how to cover it up, Rin-chan stepped
-on my foot.</t>
+          <t>As I was thinking how to cover it up, Rin-chan
+stepped on my foot.</t>
         </is>
       </c>
       <c r="C4318" t="n">
@@ -66884,8 +66932,8 @@
       </c>
       <c r="B4328" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan tilted her head and watched how things would
-play out.</t>
+          <t>Nono-chan tilted her head and watched how things
+would play out.</t>
         </is>
       </c>
       <c r="C4328" t="n">
@@ -67083,8 +67131,9 @@
       </c>
       <c r="B4341" s="1" t="inlineStr">
         <is>
-          <t>They seemed curious about what Rin-chan and I had been
-doing, but actually they weren't that interested.</t>
+          <t>They seemed curious about what Rin-chan and I had
+been doing, but actually they weren't that
+interested.</t>
         </is>
       </c>
       <c r="C4341" t="n">
@@ -67236,8 +67285,9 @@
       </c>
       <c r="B4351" s="1" t="inlineStr">
         <is>
-          <t>By the time we got off the ferry and rode the bus back
-to the dorm, everyone was already completely sleepy.</t>
+          <t>By the time we got off the ferry and rode the bus
+back to the dorm, everyone was already completely
+sleepy.</t>
         </is>
       </c>
       <c r="C4351" t="n">
@@ -67449,8 +67499,8 @@
       </c>
       <c r="B4365" s="1" t="inlineStr">
         <is>
-          <t>I still had to put our things down and the like, but I
-didn't say that and instead urged everyone on.</t>
+          <t>I still had to put our things down and the like, but
+I didn't say that and instead urged everyone on.</t>
         </is>
       </c>
       <c r="C4365" t="n">
@@ -67557,8 +67607,8 @@
       </c>
       <c r="B4372" s="1" t="inlineStr">
         <is>
-          <t>「Ah... no, Oji-sama must be tired too, so it's fine to
-do it tomorrow.」</t>
+          <t>「Ah... no, Oji-sama must be tired too, so it's fine
+to do it tomorrow.」</t>
         </is>
       </c>
       <c r="C4372" t="n">
@@ -67590,7 +67640,8 @@
       <c r="B4374" s="1" t="inlineStr">
         <is>
           <t>She's probably torn inside between sleepiness and her
-punctual habit, or perhaps a streak of fastidiousness.</t>
+punctual habit, or perhaps a streak of
+fastidiousness.</t>
         </is>
       </c>
       <c r="C4374" t="n">
